--- a/Codelist Excel Files and Conversion Templates to XML/settlementEfficacyDefinition.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/settlementEfficacyDefinition.xlsx
@@ -985,7 +985,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Codes for which definition a diggs:RITreatedAreaDesignType/diggs:settlementEfficacy value uses. UNLIKE loadEfficacyDefinition, this vocabulary is NOT drawn from an explicit list in the schema's own documentation - the two entries here are standard ground-improvement settlement-ratio definitions proposed as a reasonable starting set, not a verbatim citation. Flagged for SME confirmation before relying on this list as closed, the same caveat this project already attaches to diggs:archingModel and diggs:measurementKind. Used for the value of diggs:RITreatedAreaDesignType/diggs:settlementEfficacyDefinition.</t>
+          <t>Codes for which definition a diggs:DesignRITreatedAreaType/diggs:settlementEfficacy value uses. UNLIKE loadEfficacyDefinition, this vocabulary is NOT drawn from an explicit list in the schema's own documentation - the two entries here are standard ground-improvement settlement-ratio definitions proposed as a reasonable starting set, not a verbatim citation. Flagged for SME confirmation before relying on this list as closed, the same caveat this project already attaches to diggs:archingModel and diggs:measurementKind. Used for the value of diggs:DesignRITreatedAreaType/diggs:settlementEfficacyDefinition.</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>//diggs:RITreatedAreaDesign/diggs:settlementEfficacyDefinition</t>
+          <t>//diggs:DesignRITreatedArea/diggs:settlementEfficacyDefinition</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>//diggs:RITreatedAreaDesign/diggs:settlementEfficacyDefinition</t>
+          <t>//diggs:DesignRITreatedArea/diggs:settlementEfficacyDefinition</t>
         </is>
       </c>
     </row>
